--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4060,6 +4060,134 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120140351</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90070</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>256840</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lilafotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramaria fennica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ricken</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lugnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>707922</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6649094</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nordsluttning med kalkbarrskog ovanför hasselbestånd på lägra mark.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90070</v>
+        <v>90087</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
+          <t>Kristina Jiselmark, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristina Jiselmark, Kristoffer Stighäll</t>
+          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90190</v>
+        <v>90200</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90200</v>
+        <v>90212</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristina Jiselmark, Kristoffer Stighäll</t>
+          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90212</v>
+        <v>90213</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90213</v>
+        <v>90216</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90216</v>
+        <v>90222</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
+          <t>Kristina Jiselmark, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90222</v>
+        <v>90223</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristina Jiselmark, Kristoffer Stighäll</t>
+          <t>Kristoffer Stighäll, Kristina Jiselmark</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">

--- a/artfynd/A 32254-2020 artfynd.xlsx
+++ b/artfynd/A 32254-2020 artfynd.xlsx
@@ -4065,7 +4065,7 @@
         <v>120140351</v>
       </c>
       <c r="B30" t="n">
-        <v>90223</v>
+        <v>90230</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
